--- a/Teams.xlsx
+++ b/Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Кекс\Downloads\Telegram Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE3E6AD-01D5-4095-8596-905181004E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5075426-6037-4BB3-B39D-B531E04C2324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,21 @@
     <sheet name="ОМО_4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ОМО_4!$A$1:$E$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ОМО_4!$A$1:$H$83</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="132">
   <si>
     <t>#</t>
   </si>
@@ -418,6 +429,12 @@
   </si>
   <si>
     <t>Линейный дискриминантный анализ</t>
+  </si>
+  <si>
+    <t>Баллы за презентацию</t>
+  </si>
+  <si>
+    <t>Сумма баллов</t>
   </si>
 </sst>
 </file>
@@ -443,7 +460,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,6 +471,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -469,13 +492,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -603,17 +630,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="70.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,11 +658,20 @@
       <c r="E1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="4">
         <v>46279</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I1" s="4">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>54</v>
       </c>
@@ -649,8 +687,12 @@
       <c r="E2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <f>SUM(G2:U2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>59</v>
       </c>
@@ -666,8 +708,12 @@
       <c r="E3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="0">SUM(G3:U3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>51</v>
       </c>
@@ -683,8 +729,15 @@
       <c r="E4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>66</v>
       </c>
@@ -700,8 +753,12 @@
       <c r="E5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>24</v>
       </c>
@@ -717,8 +774,12 @@
       <c r="E6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>43</v>
       </c>
@@ -734,8 +795,12 @@
       <c r="E7" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>22</v>
       </c>
@@ -751,11 +816,13 @@
       <c r="E8" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>28</v>
       </c>
@@ -771,11 +838,13 @@
       <c r="E9" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -791,11 +860,18 @@
       <c r="E10" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>21</v>
       </c>
@@ -811,11 +887,18 @@
       <c r="E11" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>4</v>
       </c>
@@ -831,8 +914,17 @@
       <c r="E12" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>17</v>
       </c>
@@ -848,8 +940,13 @@
       <c r="E13" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>56</v>
       </c>
@@ -865,8 +962,12 @@
       <c r="E14" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>68</v>
       </c>
@@ -882,8 +983,12 @@
       <c r="E15" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>48</v>
       </c>
@@ -899,8 +1004,17 @@
       <c r="E16" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>67</v>
       </c>
@@ -916,8 +1030,13 @@
       <c r="E17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>46</v>
       </c>
@@ -933,8 +1052,12 @@
       <c r="E18" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>65</v>
       </c>
@@ -950,8 +1073,12 @@
       <c r="E19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
@@ -967,8 +1094,16 @@
       <c r="E20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <f>1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>38</v>
       </c>
@@ -984,8 +1119,16 @@
       <c r="E21" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <f>1+2</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>7</v>
       </c>
@@ -1001,8 +1144,12 @@
       <c r="E22" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1018,8 +1165,12 @@
       <c r="E23" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>13</v>
       </c>
@@ -1035,8 +1186,16 @@
       <c r="E24" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <f>1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>19</v>
       </c>
@@ -1052,8 +1211,16 @@
       <c r="E25" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <f>1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>73</v>
       </c>
@@ -1069,8 +1236,13 @@
       <c r="E26" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>76</v>
       </c>
@@ -1086,8 +1258,17 @@
       <c r="E27" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>53</v>
       </c>
@@ -1103,8 +1284,12 @@
       <c r="E28" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>60</v>
       </c>
@@ -1120,8 +1305,12 @@
       <c r="E29" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>6</v>
       </c>
@@ -1137,8 +1326,12 @@
       <c r="E30" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>20</v>
       </c>
@@ -1154,8 +1347,12 @@
       <c r="E31" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>52</v>
       </c>
@@ -1171,8 +1368,12 @@
       <c r="E32" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>55</v>
       </c>
@@ -1188,13 +1389,17 @@
       <c r="E33" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -1205,13 +1410,17 @@
       <c r="E34" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
@@ -1222,13 +1431,17 @@
       <c r="E35" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1239,13 +1452,17 @@
       <c r="E36" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1256,8 +1473,12 @@
       <c r="E37" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>29</v>
       </c>
@@ -1273,8 +1494,12 @@
       <c r="E38" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>42</v>
       </c>
@@ -1290,8 +1515,12 @@
       <c r="E39" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1307,11 +1536,18 @@
       <c r="E40" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>50</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>5</v>
       </c>
@@ -1327,19 +1563,26 @@
       <c r="E41" t="s">
         <v>110</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>50</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D42">
         <v>21</v>
@@ -1347,16 +1590,21 @@
       <c r="E42" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D43">
         <v>21</v>
@@ -1364,8 +1612,13 @@
       <c r="E43" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>26</v>
       </c>
@@ -1381,8 +1634,12 @@
       <c r="E44" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>31</v>
       </c>
@@ -1398,16 +1655,20 @@
       <c r="E45" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D46">
         <v>23</v>
@@ -1415,16 +1676,20 @@
       <c r="E46" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D47">
         <v>23</v>
@@ -1432,8 +1697,12 @@
       <c r="E47" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>49</v>
       </c>
@@ -1449,8 +1718,12 @@
       <c r="E48" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>58</v>
       </c>
@@ -1466,16 +1739,20 @@
       <c r="E49" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>25</v>
@@ -1483,16 +1760,20 @@
       <c r="E50" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D51">
         <v>25</v>
@@ -1500,8 +1781,12 @@
       <c r="E51" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>34</v>
       </c>
@@ -1517,8 +1802,12 @@
       <c r="E52" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>41</v>
       </c>
@@ -1534,8 +1823,12 @@
       <c r="E53" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>77</v>
       </c>
@@ -1551,8 +1844,12 @@
       <c r="E54" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>78</v>
       </c>
@@ -1568,8 +1865,12 @@
       <c r="E55" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>30</v>
       </c>
@@ -1585,8 +1886,13 @@
       <c r="E56" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>40</v>
       </c>
@@ -1602,8 +1908,13 @@
       <c r="E57" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>3</v>
       </c>
@@ -1619,8 +1930,12 @@
       <c r="E58" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>10</v>
       </c>
@@ -1636,8 +1951,12 @@
       <c r="E59" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>23</v>
       </c>
@@ -1653,8 +1972,12 @@
       <c r="E60" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>35</v>
       </c>
@@ -1670,8 +1993,12 @@
       <c r="E61" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>62</v>
       </c>
@@ -1687,8 +2014,12 @@
       <c r="E62" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>63</v>
       </c>
@@ -1704,8 +2035,12 @@
       <c r="E63" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>27</v>
       </c>
@@ -1721,8 +2056,12 @@
       <c r="E64" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -1738,8 +2077,12 @@
       <c r="E65" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>37</v>
       </c>
@@ -1755,8 +2098,12 @@
       <c r="E66" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>44</v>
       </c>
@@ -1772,8 +2119,12 @@
       <c r="E67" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F67">
+        <f t="shared" ref="F67:F83" si="1">SUM(G67:U67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>70</v>
       </c>
@@ -1789,8 +2140,12 @@
       <c r="E68" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>79</v>
       </c>
@@ -1806,8 +2161,12 @@
       <c r="E69" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F69">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>12</v>
       </c>
@@ -1823,8 +2182,12 @@
       <c r="E70" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>16</v>
       </c>
@@ -1840,8 +2203,12 @@
       <c r="E71" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1857,8 +2224,16 @@
       <c r="E72" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F72">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H72">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>74</v>
       </c>
@@ -1874,8 +2249,16 @@
       <c r="E73" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F73">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <f>1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>80</v>
       </c>
@@ -1891,8 +2274,12 @@
       <c r="E74" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F74">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>81</v>
       </c>
@@ -1908,8 +2295,12 @@
       <c r="E75" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>57</v>
       </c>
@@ -1925,8 +2316,12 @@
       <c r="E76" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>61</v>
       </c>
@@ -1942,13 +2337,17 @@
       <c r="E77" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
@@ -1956,13 +2355,17 @@
       <c r="D78">
         <v>39</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F78">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -1970,41 +2373,57 @@
       <c r="D79">
         <v>39</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
+        <v>47</v>
+      </c>
+      <c r="B80" t="s">
+        <v>70</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81">
         <v>25</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>53</v>
       </c>
-      <c r="C80" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81">
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82">
         <v>33</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>60</v>
       </c>
-      <c r="C81" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>47</v>
-      </c>
-      <c r="B82" t="s">
-        <v>70</v>
-      </c>
       <c r="C82" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2014,10 +2433,14 @@
       <c r="C83" t="s">
         <v>32</v>
       </c>
+      <c r="F83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E83" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E83">
+  <autoFilter ref="A1:H83" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H83">
       <sortCondition ref="D1:D83"/>
     </sortState>
   </autoFilter>
